--- a/basedatos_partidas/salida/descompuestos/DRC010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/DRC010.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H22"/>
+  <dimension ref="A3:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -464,14 +464,14 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Picado de revestimiento cerámico en paramento y su capa de agarre.</t>
+          <t>Picado de enchapado cerámico en pared y su capa de pega.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Picado de revestimiento cerámico existente en paramento vertical, incluida su capa de agarre de mortero, ejecutado con martillo eléctrico manual hasta dejar el soporte a la vista, sin comprometer la estabilidad del muro ni dañar las instalaciones empotradas. Incluye protección previa de pisos, aparatos y carpintería, control de polvo mediante aspiración, retirada manual de escombro en sacos hasta el punto de acopio y limpieza de la superficie resultante, dejándola preparada para recibir el nuevo friso. No incluye el transporte a vertedero. Medido en superficie realmente picada.
+          <t xml:space="preserve">Picado de enchapado cerámico o de porcelanato existente en pared, incluida su capa de pega de mortero, ejecutado con martillo eléctrico manual hasta dejar el friso o el bloque a la vista, sin comprometer la estabilidad del muro ni dañar las tuberías y canalizaciones empotradas. Incluye la localización previa de las instalaciones que discurren por el paramento, la protección de pisos, aparatos y puertas, el control de polvo mediante aspiración, el retiro manual del escombro en sacos hasta el punto de acopio y la limpieza de la superficie, dejándola lista para recibir el nuevo friso. No incluye el bote del escombro, que se valora en el capítulo de gestión de residuos. Medido en superficie realmente picada.
 </t>
         </is>
       </c>
@@ -546,204 +546,256 @@
       </c>
     </row>
     <row r="11">
-      <c r="F11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MT-CONS-DEM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Consumibles de demolición: puntas y cinceles de martillo, discos de corte y hojas de espátula.</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MT-PROT-OBRA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Protección de obra con plástico, cartón corrugado y cinta de enmascarar.</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t>Subtotal materiales:</t>
         </is>
       </c>
-      <c r="H11" t="n">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="H13" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="1" t="inlineStr">
+      <c r="E14" s="1" t="inlineStr">
         <is>
           <t>Equipo y maquinaria</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>MQ-MART-ELEC</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Martillo eléctrico de demolición de 5 kg, incluida amortización y consumo.</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F15" t="n">
         <v>0.3</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G15" t="n">
         <v>3.9</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H15" t="n">
         <v>1.17</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>MQ-ASPIR</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Aspirador industrial con filtro de polvo fino para limpieza de soporte y control de polvo.</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="F16" t="n">
         <v>0.14</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G16" t="n">
         <v>2.1</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H16" t="n">
         <v>0.29</v>
       </c>
     </row>
-    <row r="15">
-      <c r="F15" s="1" t="inlineStr">
+    <row r="17">
+      <c r="F17" s="1" t="inlineStr">
         <is>
           <t>Subtotal equipo y maquinaria:</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="H17" t="n">
         <v>1.46</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="18">
+      <c r="A18" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="1" t="inlineStr">
+      <c r="E18" s="1" t="inlineStr">
         <is>
           <t>Mano de obra</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>MO-AYU-ESP</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Ayudante especializado.</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F19" t="n">
         <v>0.35</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G19" t="n">
         <v>4</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H19" t="n">
         <v>1.4</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>MO-AYU</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Ayudante.</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F20" t="n">
         <v>0.35</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G20" t="n">
         <v>3.5</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H20" t="n">
         <v>1.22</v>
       </c>
     </row>
-    <row r="19">
-      <c r="F19" s="1" t="inlineStr">
+    <row r="21">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>Subtotal mano de obra:</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="H21" t="n">
         <v>2.62</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="22">
+      <c r="A22" t="n">
         <v>4</v>
       </c>
-      <c r="E20" s="1" t="inlineStr">
+      <c r="E22" s="1" t="inlineStr">
         <is>
           <t>Costes directos complementarios</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="D21" t="inlineStr">
+    <row r="23">
+      <c r="D23" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Costes directos complementarios</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G21" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="H21" t="n">
+      <c r="G23" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="H23" t="n">
         <v>0.05</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Costes directos (1+2+3+4):</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="5" t="n">
-        <v>4.58</v>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="5" t="n">
+        <v>4.81</v>
       </c>
     </row>
   </sheetData>
